--- a/outputs/7902.xlsx
+++ b/outputs/7902.xlsx
@@ -174,24 +174,28 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="19" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="19" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -450,203 +454,203 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="16.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="14.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="14.5"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I2" s="3" t="n">
+      <c r="B2" s="3"/>
+      <c r="C2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I2" s="4" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D3" s="3" t="n">
+      <c r="B3" s="3"/>
+      <c r="C3" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D3" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I3" s="3" t="n">
+      <c r="F3" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3" t="n">
+      <c r="B4" s="3"/>
+      <c r="C4" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I4" s="3" t="n">
+      <c r="D4" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I4" s="4" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="4" t="n">
         <v>0.12</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>0.13</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H5" s="3" t="n">
+      <c r="E5" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I5" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I6" s="3" t="n">
+      <c r="G6" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I6" s="4" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I7" s="3" t="n">
+      <c r="C7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I7" s="4" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -669,299 +673,299 @@
   <dimension ref="B2:T6"/>
   <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="16.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8.16"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="20" min="12" style="0" width="8.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8.16"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="20" min="12" style="1" width="8.84"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="T2" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="3" t="n">
-        <f aca="false">IF($B3="",VLOOKUP($C3,Grouping!$A$2:$I$7,3,FALSE()),VLOOKUP($B3,Grouping!$B$2:$I$7,2,FALSE()))</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <f aca="false">IF($B3="",VLOOKUP($C3,Grouping!$A$2:$I$7,4,FALSE()),VLOOKUP($B3,Grouping!$B$2:$I$7,3,FALSE()))</f>
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <f aca="false">IF($B3="",VLOOKUP($C3,Grouping!$A$2:$I$7,5,FALSE()),VLOOKUP($B3,Grouping!$B$2:$I$7,4,FALSE()))</f>
-        <v>0.5</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <f aca="false">IF($B3="",VLOOKUP($C3,Grouping!$A$2:$I$7,6,FALSE()),VLOOKUP($B3,Grouping!$B$2:$I$7,5,FALSE()))</f>
-        <v>0.5</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <f aca="false">IF($B3="",VLOOKUP($C3,Grouping!$A$2:$I$7,7,FALSE()),VLOOKUP($B3,Grouping!$B$2:$I$7,6,FALSE()))</f>
-        <v>0.5</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <f aca="false">IF($B3="",VLOOKUP($C3,Grouping!$A$2:$I$7,8,FALSE()),VLOOKUP($B3,Grouping!$B$2:$I$7,7,FALSE()))</f>
-        <v>0.5</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <f aca="false">IF($B3="",VLOOKUP($C3,Grouping!$A$2:$I$7,9,FALSE()),VLOOKUP($B3,Grouping!$B$2:$I$7,8,FALSE()))</f>
-        <v>0.5</v>
-      </c>
-      <c r="L3" s="4" t="n">
+      <c r="D3" s="4" t="n">
+        <f aca="false">IF(B3="",VLOOKUP(C3,Grouping!$A$2:$I$7,3,FALSE()),VLOOKUP(B3,Grouping!$B$2:$I$7,2,FALSE()))</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <f aca="false">IF(B3="",VLOOKUP(C3,Grouping!$A$2:$I$7,4,FALSE()),VLOOKUP(B3,Grouping!$B$2:$I$7,3,FALSE()))</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <f aca="false">IF(B3="",VLOOKUP(C3,Grouping!$A$2:$I$7,5,FALSE()),VLOOKUP(B3,Grouping!$B$2:$I$7,4,FALSE()))</f>
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <f aca="false">IF(B3="",VLOOKUP(C3,Grouping!$A$2:$I$7,6,FALSE()),VLOOKUP(B3,Grouping!$B$2:$I$7,5,FALSE()))</f>
+        <v>0.5</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <f aca="false">IF(B3="",VLOOKUP(C3,Grouping!$A$2:$I$7,7,FALSE()),VLOOKUP(B3,Grouping!$B$2:$I$7,6,FALSE()))</f>
+        <v>0.5</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <f aca="false">IF(B3="",VLOOKUP(C3,Grouping!$A$2:$I$7,8,FALSE()),VLOOKUP(B3,Grouping!$B$2:$I$7,7,FALSE()))</f>
+        <v>0.5</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <f aca="false">IF(B3="",VLOOKUP(C3,Grouping!$A$2:$I$7,9,FALSE()),VLOOKUP(B3,Grouping!$B$2:$I$7,8,FALSE()))</f>
+        <v>0.5</v>
+      </c>
+      <c r="L3" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="M3" s="4" t="n">
+      <c r="M3" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="N3" s="4" t="n">
+      <c r="N3" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="O3" s="5" t="n">
         <v>400</v>
       </c>
-      <c r="P3" s="4" t="n">
+      <c r="P3" s="5" t="n">
         <v>5600</v>
       </c>
-      <c r="Q3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" s="4" t="n">
+      <c r="Q3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="5" t="n">
         <v>10000</v>
       </c>
-      <c r="T3" s="3" t="n">
+      <c r="T3" s="4" t="n">
         <f aca="false">+D3*L3</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="3" t="n">
-        <f aca="false">IF($B4="",VLOOKUP($C4,Grouping!$A$2:$I$7,3,FALSE()),VLOOKUP($B4,Grouping!$B$2:$I$7,2,FALSE()))</f>
+      <c r="D4" s="4" t="n">
+        <f aca="false">IF(B4="",VLOOKUP(C4,Grouping!$A$2:$I$7,3,FALSE()),VLOOKUP(B4,Grouping!$B$2:$I$7,2,FALSE()))</f>
         <v>0.12</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <f aca="false">IF($B4="",VLOOKUP($C4,Grouping!$A$2:$I$7,4,FALSE()),VLOOKUP($B4,Grouping!$B$2:$I$7,3,FALSE()))</f>
+      <c r="E4" s="4" t="n">
+        <f aca="false">IF(B4="",VLOOKUP(C4,Grouping!$A$2:$I$7,4,FALSE()),VLOOKUP(B4,Grouping!$B$2:$I$7,3,FALSE()))</f>
         <v>0.13</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <f aca="false">IF($B4="",VLOOKUP($C4,Grouping!$A$2:$I$7,5,FALSE()),VLOOKUP($B4,Grouping!$B$2:$I$7,4,FALSE()))</f>
-        <v>0.5</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <f aca="false">IF($B4="",VLOOKUP($C4,Grouping!$A$2:$I$7,6,FALSE()),VLOOKUP($B4,Grouping!$B$2:$I$7,5,FALSE()))</f>
-        <v>0.5</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <f aca="false">IF($B4="",VLOOKUP($C4,Grouping!$A$2:$I$7,7,FALSE()),VLOOKUP($B4,Grouping!$B$2:$I$7,6,FALSE()))</f>
-        <v>0.5</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <f aca="false">IF($B4="",VLOOKUP($C4,Grouping!$A$2:$I$7,8,FALSE()),VLOOKUP($B4,Grouping!$B$2:$I$7,7,FALSE()))</f>
+      <c r="F4" s="4" t="n">
+        <f aca="false">IF(B4="",VLOOKUP(C4,Grouping!$A$2:$I$7,5,FALSE()),VLOOKUP(B4,Grouping!$B$2:$I$7,4,FALSE()))</f>
+        <v>0.5</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <f aca="false">IF(B4="",VLOOKUP(C4,Grouping!$A$2:$I$7,6,FALSE()),VLOOKUP(B4,Grouping!$B$2:$I$7,5,FALSE()))</f>
+        <v>0.5</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <f aca="false">IF(B4="",VLOOKUP(C4,Grouping!$A$2:$I$7,7,FALSE()),VLOOKUP(B4,Grouping!$B$2:$I$7,6,FALSE()))</f>
+        <v>0.5</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <f aca="false">IF(B4="",VLOOKUP(C4,Grouping!$A$2:$I$7,8,FALSE()),VLOOKUP(B4,Grouping!$B$2:$I$7,7,FALSE()))</f>
         <v>0.75</v>
       </c>
-      <c r="J4" s="3" t="n">
-        <f aca="false">IF($B4="",VLOOKUP($C4,Grouping!$A$2:$I$7,9,FALSE()),VLOOKUP($B4,Grouping!$B$2:$I$7,8,FALSE()))</f>
+      <c r="J4" s="4" t="n">
+        <f aca="false">IF(B4="",VLOOKUP(C4,Grouping!$A$2:$I$7,9,FALSE()),VLOOKUP(B4,Grouping!$B$2:$I$7,8,FALSE()))</f>
         <v>1</v>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="L4" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="M4" s="4" t="n">
+      <c r="M4" s="5" t="n">
         <v>170</v>
       </c>
-      <c r="N4" s="4" t="n">
+      <c r="N4" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="O4" s="4" t="n">
+      <c r="O4" s="5" t="n">
         <v>325</v>
       </c>
-      <c r="P4" s="4" t="n">
+      <c r="P4" s="5" t="n">
         <v>4000</v>
       </c>
-      <c r="Q4" s="4" t="n">
+      <c r="Q4" s="5" t="n">
         <v>5000</v>
       </c>
-      <c r="R4" s="4" t="n">
+      <c r="R4" s="5" t="n">
         <v>40000</v>
       </c>
-      <c r="T4" s="3" t="n">
+      <c r="T4" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="2"/>
-      <c r="C5" s="2" t="s">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="3" t="n">
-        <f aca="false">IF($B5="",VLOOKUP($C5,Grouping!$A$2:$I$7,3,FALSE()),VLOOKUP($B5,Grouping!$B$2:$I$7,2,FALSE()))</f>
+      <c r="D5" s="4" t="n">
+        <f aca="false">IF(B5="",VLOOKUP(C5,Grouping!$A$2:$I$7,3,FALSE()),VLOOKUP(B5,Grouping!$B$2:$I$7,2,FALSE()))</f>
         <v>0.05</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <f aca="false">IF($B5="",VLOOKUP($C5,Grouping!$A$2:$I$7,4,FALSE()),VLOOKUP($B5,Grouping!$B$2:$I$7,3,FALSE()))</f>
-        <v>0.1</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <f aca="false">IF($B5="",VLOOKUP($C5,Grouping!$A$2:$I$7,5,FALSE()),VLOOKUP($B5,Grouping!$B$2:$I$7,4,FALSE()))</f>
-        <v>0.1</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <f aca="false">IF($B5="",VLOOKUP($C5,Grouping!$A$2:$I$7,6,FALSE()),VLOOKUP($B5,Grouping!$B$2:$I$7,5,FALSE()))</f>
-        <v>0.1</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <f aca="false">IF($B5="",VLOOKUP($C5,Grouping!$A$2:$I$7,7,FALSE()),VLOOKUP($B5,Grouping!$B$2:$I$7,6,FALSE()))</f>
-        <v>0.1</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <f aca="false">IF($B5="",VLOOKUP($C5,Grouping!$A$2:$I$7,8,FALSE()),VLOOKUP($B5,Grouping!$B$2:$I$7,7,FALSE()))</f>
-        <v>0.1</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <f aca="false">IF($B5="",VLOOKUP($C5,Grouping!$A$2:$I$7,9,FALSE()),VLOOKUP($B5,Grouping!$B$2:$I$7,8,FALSE()))</f>
-        <v>0.1</v>
-      </c>
-      <c r="L5" s="4" t="n">
+      <c r="E5" s="4" t="n">
+        <f aca="false">IF(B5="",VLOOKUP(C5,Grouping!$A$2:$I$7,4,FALSE()),VLOOKUP(B5,Grouping!$B$2:$I$7,3,FALSE()))</f>
+        <v>0.1</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <f aca="false">IF(B5="",VLOOKUP(C5,Grouping!$A$2:$I$7,5,FALSE()),VLOOKUP(B5,Grouping!$B$2:$I$7,4,FALSE()))</f>
+        <v>0.1</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <f aca="false">IF(B5="",VLOOKUP(C5,Grouping!$A$2:$I$7,6,FALSE()),VLOOKUP(B5,Grouping!$B$2:$I$7,5,FALSE()))</f>
+        <v>0.1</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <f aca="false">IF(B5="",VLOOKUP(C5,Grouping!$A$2:$I$7,7,FALSE()),VLOOKUP(B5,Grouping!$B$2:$I$7,6,FALSE()))</f>
+        <v>0.1</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <f aca="false">IF(B5="",VLOOKUP(C5,Grouping!$A$2:$I$7,8,FALSE()),VLOOKUP(B5,Grouping!$B$2:$I$7,7,FALSE()))</f>
+        <v>0.1</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <f aca="false">IF(B5="",VLOOKUP(C5,Grouping!$A$2:$I$7,9,FALSE()),VLOOKUP(B5,Grouping!$B$2:$I$7,8,FALSE()))</f>
+        <v>0.1</v>
+      </c>
+      <c r="L5" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="M5" s="4" t="n">
+      <c r="M5" s="5" t="n">
         <v>180</v>
       </c>
-      <c r="N5" s="4" t="n">
+      <c r="N5" s="5" t="n">
         <v>280</v>
       </c>
-      <c r="O5" s="4" t="n">
+      <c r="O5" s="5" t="n">
         <v>350</v>
       </c>
-      <c r="P5" s="4" t="n">
+      <c r="P5" s="5" t="n">
         <v>4500</v>
       </c>
-      <c r="Q5" s="4" t="n">
+      <c r="Q5" s="5" t="n">
         <v>10000</v>
       </c>
-      <c r="R5" s="4" t="n">
+      <c r="R5" s="5" t="n">
         <v>30000</v>
       </c>
-      <c r="T5" s="3" t="n">
+      <c r="T5" s="4" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="3" t="n">
-        <f aca="false">IF($B6="",VLOOKUP($C6,Grouping!$A$2:$I$7,3,FALSE()),VLOOKUP($B6,Grouping!$B$2:$I$7,2,FALSE()))</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <f aca="false">IF($B6="",VLOOKUP($C6,Grouping!$A$2:$I$7,4,FALSE()),VLOOKUP($B6,Grouping!$B$2:$I$7,3,FALSE()))</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <f aca="false">IF($B6="",VLOOKUP($C6,Grouping!$A$2:$I$7,5,FALSE()),VLOOKUP($B6,Grouping!$B$2:$I$7,4,FALSE()))</f>
-        <v>0.1</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <f aca="false">IF($B6="",VLOOKUP($C6,Grouping!$A$2:$I$7,6,FALSE()),VLOOKUP($B6,Grouping!$B$2:$I$7,5,FALSE()))</f>
-        <v>0.1</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <f aca="false">IF($B6="",VLOOKUP($C6,Grouping!$A$2:$I$7,7,FALSE()),VLOOKUP($B6,Grouping!$B$2:$I$7,6,FALSE()))</f>
-        <v>0.1</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <f aca="false">IF($B6="",VLOOKUP($C6,Grouping!$A$2:$I$7,8,FALSE()),VLOOKUP($B6,Grouping!$B$2:$I$7,7,FALSE()))</f>
-        <v>0.1</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <f aca="false">IF($B6="",VLOOKUP($C6,Grouping!$A$2:$I$7,9,FALSE()),VLOOKUP($B6,Grouping!$B$2:$I$7,8,FALSE()))</f>
-        <v>0.1</v>
-      </c>
-      <c r="L6" s="4" t="n">
+      <c r="D6" s="4" t="n">
+        <f aca="false">IF(B6="",VLOOKUP(C6,Grouping!$A$2:$I$7,3,FALSE()),VLOOKUP(B6,Grouping!$B$2:$I$7,2,FALSE()))</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <f aca="false">IF(B6="",VLOOKUP(C6,Grouping!$A$2:$I$7,4,FALSE()),VLOOKUP(B6,Grouping!$B$2:$I$7,3,FALSE()))</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <f aca="false">IF(B6="",VLOOKUP(C6,Grouping!$A$2:$I$7,5,FALSE()),VLOOKUP(B6,Grouping!$B$2:$I$7,4,FALSE()))</f>
+        <v>0.1</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <f aca="false">IF(B6="",VLOOKUP(C6,Grouping!$A$2:$I$7,6,FALSE()),VLOOKUP(B6,Grouping!$B$2:$I$7,5,FALSE()))</f>
+        <v>0.1</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <f aca="false">IF(B6="",VLOOKUP(C6,Grouping!$A$2:$I$7,7,FALSE()),VLOOKUP(B6,Grouping!$B$2:$I$7,6,FALSE()))</f>
+        <v>0.1</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <f aca="false">IF(B6="",VLOOKUP(C6,Grouping!$A$2:$I$7,8,FALSE()),VLOOKUP(B6,Grouping!$B$2:$I$7,7,FALSE()))</f>
+        <v>0.1</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <f aca="false">IF(B6="",VLOOKUP(C6,Grouping!$A$2:$I$7,9,FALSE()),VLOOKUP(B6,Grouping!$B$2:$I$7,8,FALSE()))</f>
+        <v>0.1</v>
+      </c>
+      <c r="L6" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="M6" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="N6" s="4" t="n">
+      <c r="N6" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="O6" s="4" t="n">
+      <c r="O6" s="5" t="n">
         <v>275</v>
       </c>
-      <c r="P6" s="4" t="n">
+      <c r="P6" s="5" t="n">
         <v>2500</v>
       </c>
-      <c r="Q6" s="4" t="n">
+      <c r="Q6" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="R6" s="4" t="n">
+      <c r="R6" s="5" t="n">
         <v>60000</v>
       </c>
-      <c r="T6" s="3" t="n">
+      <c r="T6" s="4" t="n">
         <v>0.1</v>
       </c>
     </row>
